--- a/src/Calculators.CashFlow.Tests/ExcelReader/Files/einkauf.xlsx
+++ b/src/Calculators.CashFlow.Tests/ExcelReader/Files/einkauf.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\repos\PensionTools\src\Calculators.CashFlow.Tests\ExcelReader\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7885505-9EC7-41EA-9B7F-961D74AE1D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9C7FA8-3E00-4B6C-9E75-2ABEF5367423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33555" yWindow="525" windowWidth="14670" windowHeight="19200" tabRatio="598" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="870" yWindow="60" windowWidth="32520" windowHeight="19200" tabRatio="598" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Person" sheetId="4" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="64">
   <si>
     <t>ID</t>
   </si>
@@ -214,6 +214,27 @@
   </si>
   <si>
     <t>Steuerfluss</t>
+  </si>
+  <si>
+    <t>Nummer</t>
+  </si>
+  <si>
+    <t>Geschlecht</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>Geburtsdatum</t>
+  </si>
+  <si>
+    <t>Verheiratet</t>
+  </si>
+  <si>
+    <t>Reformiert</t>
   </si>
 </sst>
 </file>
@@ -574,41 +595,57 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9246EE65-0125-4D81-8881-133F24534DB9}">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C1" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="E1" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="G1" s="6" t="s">
         <v>22</v>
       </c>
     </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" t="s">
+        <v>63</v>
+      </c>
+    </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{50B90021-A4A0-45A1-A53D-DCC133D7E961}">
-      <formula1>"Alleinstehend, Verheiratet"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3" xr:uid="{736DE558-003D-4DA5-AF6A-2C1D3A15E6CD}">
-      <formula1>"Reformiert, Katholisch, Römisch-Katholisch, Andere"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/src/Calculators.CashFlow.Tests/ExcelReader/Files/einkauf.xlsx
+++ b/src/Calculators.CashFlow.Tests/ExcelReader/Files/einkauf.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\repos\PensionTools\src\Calculators.CashFlow.Tests\ExcelReader\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9C7FA8-3E00-4B6C-9E75-2ABEF5367423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061AD709-E38F-43CA-A9DF-9DD79C4AFF7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="870" yWindow="60" windowWidth="32520" windowHeight="19200" tabRatio="598" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21075" yWindow="480" windowWidth="19485" windowHeight="19200" tabRatio="598" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Person" sheetId="4" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="63">
   <si>
     <t>ID</t>
   </si>
@@ -60,21 +60,12 @@
     <t>Enddatum</t>
   </si>
   <si>
-    <t>Gemeindename</t>
-  </si>
-  <si>
-    <t>PLZ</t>
-  </si>
-  <si>
     <t>Kanton</t>
   </si>
   <si>
     <t>ZH</t>
   </si>
   <si>
-    <t>Zürich</t>
-  </si>
-  <si>
     <t>Name</t>
   </si>
   <si>
@@ -235,6 +226,12 @@
   </si>
   <si>
     <t>Reformiert</t>
+  </si>
+  <si>
+    <t>Gemeinde Id</t>
+  </si>
+  <si>
+    <t>Steuer-Id</t>
   </si>
 </sst>
 </file>
@@ -306,7 +303,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -314,6 +311,8 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -607,25 +606,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -633,16 +632,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" t="s">
         <v>59</v>
       </c>
-      <c r="D2" t="s">
-        <v>62</v>
-      </c>
       <c r="E2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F2" t="s">
         <v>60</v>
-      </c>
-      <c r="F2" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -652,34 +651,33 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E29DC190-0B98-4C71-BDF8-1792310B4F6D}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>134</v>
+      </c>
+      <c r="B2" s="8">
+        <v>330400000</v>
+      </c>
+      <c r="C2" t="s">
         <v>6</v>
-      </c>
-      <c r="B2">
-        <v>8047</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -749,10 +747,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -760,10 +758,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -771,10 +769,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -782,10 +780,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -794,10 +792,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -806,10 +804,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -818,10 +816,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -830,10 +828,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -842,10 +840,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -854,10 +852,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -866,10 +864,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -878,10 +876,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -977,25 +975,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>33</v>
-      </c>
       <c r="F1" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1003,7 +1001,7 @@
         <v>45292</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -1015,10 +1013,10 @@
         <v>200000</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1026,7 +1024,7 @@
         <v>45292</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C3">
         <v>8</v>
@@ -1038,10 +1036,10 @@
         <v>80000</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1049,7 +1047,7 @@
         <v>45658</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -1061,10 +1059,10 @@
         <v>10000</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1072,7 +1070,7 @@
         <v>45292</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C5">
         <v>10</v>
@@ -1089,7 +1087,7 @@
         <v>45292</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C6">
         <v>10</v>
@@ -1106,7 +1104,7 @@
         <v>45292</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C7">
         <v>10</v>
@@ -1123,7 +1121,7 @@
         <v>45474</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C8">
         <v>11</v>
@@ -1135,10 +1133,10 @@
         <v>5000</v>
       </c>
       <c r="F8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G8" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1146,7 +1144,7 @@
         <v>45658</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -1158,10 +1156,10 @@
         <v>1600</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G9" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1169,7 +1167,7 @@
         <v>46023</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -1181,10 +1179,10 @@
         <v>1600</v>
       </c>
       <c r="F10" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G10" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1192,7 +1190,7 @@
         <v>45292</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1204,10 +1202,10 @@
         <v>50000</v>
       </c>
       <c r="F11" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G11" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1215,7 +1213,7 @@
         <v>45474</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -1227,10 +1225,10 @@
         <v>50000</v>
       </c>
       <c r="F12" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G12" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1238,7 +1236,7 @@
         <v>45658</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1250,10 +1248,10 @@
         <v>50000</v>
       </c>
       <c r="F13" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1261,7 +1259,7 @@
         <v>45839</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -1273,10 +1271,10 @@
         <v>50000</v>
       </c>
       <c r="F14" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G14" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1284,7 +1282,7 @@
         <v>46023</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -1296,10 +1294,10 @@
         <v>50000</v>
       </c>
       <c r="F15" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G15" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1307,7 +1305,7 @@
         <v>46204</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -1319,10 +1317,10 @@
         <v>50000</v>
       </c>
       <c r="F16" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G16" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1330,7 +1328,7 @@
         <v>45657</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C17">
         <v>2</v>
@@ -1342,10 +1340,10 @@
         <v>40000</v>
       </c>
       <c r="F17" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1353,7 +1351,7 @@
         <v>46022</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -1365,10 +1363,10 @@
         <v>40000</v>
       </c>
       <c r="F18" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G18" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1376,7 +1374,7 @@
         <v>46387</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C19">
         <v>2</v>
@@ -1388,10 +1386,10 @@
         <v>40000</v>
       </c>
       <c r="F19" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G19" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1413,25 +1411,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1439,7 +1437,7 @@
         <v>46387</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -1451,10 +1449,10 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1462,7 +1460,7 @@
         <v>46387</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -1474,10 +1472,10 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1499,25 +1497,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1525,7 +1523,7 @@
         <v>45292</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C2">
         <v>9</v>
@@ -1537,10 +1535,10 @@
         <v>0.02</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1548,7 +1546,7 @@
         <v>45658</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C3">
         <v>9</v>
@@ -1560,10 +1558,10 @@
         <v>0.04</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1571,7 +1569,7 @@
         <v>46023</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C4">
         <v>9</v>
@@ -1583,10 +1581,10 @@
         <v>0.01</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1608,25 +1606,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>49</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1637,10 +1635,10 @@
         <v>46387</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -1649,7 +1647,7 @@
         <v>6</v>
       </c>
       <c r="G2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1658,10 +1656,10 @@
         <v>45657</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1670,7 +1668,7 @@
         <v>6</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1679,10 +1677,10 @@
         <v>46022</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -1691,7 +1689,7 @@
         <v>6</v>
       </c>
       <c r="G4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1699,10 +1697,10 @@
         <v>46387</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -1711,7 +1709,7 @@
         <v>6</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1722,10 +1720,10 @@
         <v>45657</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" t="s">
         <v>50</v>
-      </c>
-      <c r="D6" t="s">
-        <v>53</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -1734,7 +1732,7 @@
         <v>6</v>
       </c>
       <c r="G6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1745,10 +1743,10 @@
         <v>46022</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" t="s">
         <v>50</v>
-      </c>
-      <c r="D7" t="s">
-        <v>53</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -1757,7 +1755,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1768,10 +1766,10 @@
         <v>46387</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" t="s">
         <v>50</v>
-      </c>
-      <c r="D8" t="s">
-        <v>53</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -1780,7 +1778,7 @@
         <v>6</v>
       </c>
       <c r="G8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/src/Calculators.CashFlow.Tests/ExcelReader/Files/einkauf.xlsx
+++ b/src/Calculators.CashFlow.Tests/ExcelReader/Files/einkauf.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\repos\PensionTools\src\Calculators.CashFlow.Tests\ExcelReader\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061AD709-E38F-43CA-A9DF-9DD79C4AFF7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7DB09E-E894-4BB7-B20D-34A9C2F5ECC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21075" yWindow="480" windowWidth="19485" windowHeight="19200" tabRatio="598" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14115" yWindow="135" windowWidth="26100" windowHeight="19200" tabRatio="598" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Person" sheetId="4" r:id="rId1"/>
@@ -303,7 +303,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -311,8 +311,6 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -655,14 +653,14 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="5" t="s">
         <v>62</v>
       </c>
       <c r="C1" s="5" t="s">
@@ -673,7 +671,7 @@
       <c r="A2">
         <v>134</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2">
         <v>330400000</v>
       </c>
       <c r="C2" t="s">
